--- a/artfynd/A 19324-2024 artfynd.xlsx
+++ b/artfynd/A 19324-2024 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>120851606</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>120851360</v>
       </c>
       <c r="B4" t="n">
-        <v>105161</v>
+        <v>105171</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 19324-2024 artfynd.xlsx
+++ b/artfynd/A 19324-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>78275277</v>
       </c>
       <c r="B2" t="n">
-        <v>96222</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>792366.7604430974</v>
+        <v>792367</v>
       </c>
       <c r="R2" t="n">
-        <v>7320206.324028214</v>
+        <v>7320206</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -760,19 +755,9 @@
           <t>2019-06-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-06-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -805,37 +790,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120851606</v>
+        <v>120852612</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1435</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -845,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>792375</v>
+        <v>792391</v>
       </c>
       <c r="R3" t="n">
-        <v>7320257</v>
+        <v>7320270</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,12 +875,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Klara Elmquist</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Klara Elmquist</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -911,37 +891,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120851360</v>
+        <v>120851606</v>
       </c>
       <c r="B4" t="n">
-        <v>105171</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>792368</v>
+        <v>792375</v>
       </c>
       <c r="R4" t="n">
-        <v>7320253</v>
+        <v>7320257</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,6 +985,309 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120851358</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kusberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>792377</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7320269</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Klara Elmquist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Klara Elmquist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120851360</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kusberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>792368</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7320253</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Klara Elmquist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Klara Elmquist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120851493</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99155</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kusberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>792386</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7320273</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Klara Elmquist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Klara Elmquist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>

--- a/artfynd/A 19324-2024 artfynd.xlsx
+++ b/artfynd/A 19324-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78275277</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120852612</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120851606</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120851358</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120851360</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,8 +1322,21 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120851493</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>